--- a/artfynd/A 14340-2026 artfynd.xlsx
+++ b/artfynd/A 14340-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131945220</v>
+        <v>131945204</v>
       </c>
       <c r="B2" t="n">
-        <v>57905</v>
+        <v>79886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,48 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Slåmossen, Slåmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480218</v>
+        <v>480217</v>
       </c>
       <c r="R2" t="n">
-        <v>6597841</v>
+        <v>6597826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringbarkning i tall.</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131945204</v>
+        <v>131945220</v>
       </c>
       <c r="B3" t="n">
-        <v>79886</v>
+        <v>57905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +793,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Slåmossen, Slåmossen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480217</v>
+        <v>480218</v>
       </c>
       <c r="R3" t="n">
-        <v>6597826</v>
+        <v>6597841</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14340-2026 artfynd.xlsx
+++ b/artfynd/A 14340-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131945204</v>
       </c>
       <c r="B2" t="n">
-        <v>79886</v>
+        <v>79888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131945220</v>
       </c>
       <c r="B3" t="n">
-        <v>57905</v>
+        <v>57907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14340-2026 artfynd.xlsx
+++ b/artfynd/A 14340-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131945204</v>
       </c>
       <c r="B2" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131945220</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14340-2026 artfynd.xlsx
+++ b/artfynd/A 14340-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131945204</v>
       </c>
       <c r="B2" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14340-2026 artfynd.xlsx
+++ b/artfynd/A 14340-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131945204</v>
       </c>
       <c r="B2" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131945220</v>
       </c>
       <c r="B3" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14340-2026 artfynd.xlsx
+++ b/artfynd/A 14340-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131945204</v>
       </c>
       <c r="B2" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131945220</v>
       </c>
       <c r="B3" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14340-2026 artfynd.xlsx
+++ b/artfynd/A 14340-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131945204</v>
       </c>
       <c r="B2" t="n">
-        <v>79946</v>
+        <v>79992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131945220</v>
       </c>
       <c r="B3" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,6 +905,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132318243</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>480109</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6597848</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14340-2026 artfynd.xlsx
+++ b/artfynd/A 14340-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131945204</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131945220</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,8 +1026,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318243</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>